--- a/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:17</t>
+          <t>2026-08-21 16:06:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:21</t>
+          <t>2026-08-21 16:06:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:22</t>
+          <t>2026-08-21 16:06:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:23</t>
+          <t>2026-08-21 16:06:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:38</t>
+          <t>2026-08-21 16:07:08</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:39</t>
+          <t>2026-08-21 16:07:09</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:40</t>
+          <t>2026-08-21 16:07:11</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:41</t>
+          <t>2026-08-21 16:07:12</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:46</t>
+          <t>2026-08-21 16:07:17</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:48</t>
+          <t>2026-08-21 16:07:19</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:49</t>
+          <t>2026-08-21 16:07:20</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:50</t>
+          <t>2026-08-21 16:07:21</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">

--- a/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:48</t>
+          <t>2026-08-21 16:24:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:50</t>
+          <t>2026-08-21 16:24:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:51</t>
+          <t>2026-08-21 16:24:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:52</t>
+          <t>2026-08-21 16:24:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:08</t>
+          <t>2026-08-21 16:25:02</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:09</t>
+          <t>2026-08-21 16:25:03</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:11</t>
+          <t>2026-08-21 16:25:04</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:12</t>
+          <t>2026-08-21 16:25:05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:17</t>
+          <t>2026-08-21 16:25:11</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:19</t>
+          <t>2026-08-21 16:25:13</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:20</t>
+          <t>2026-08-21 16:25:14</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:21</t>
+          <t>2026-08-21 16:25:15</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13194,6106 +13194,6 @@
         </is>
       </c>
       <c r="M209" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>2330台積電</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>+1.47%2410</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>+1.47%</t>
-        </is>
-      </c>
-      <c r="H210" t="n">
-        <v>2410</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>16.66%12,000,000</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>16.66%</t>
-        </is>
-      </c>
-      <c r="K210" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>1</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>2383台光電</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>-5.1%5680</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-5.1%</t>
-        </is>
-      </c>
-      <c r="H211" t="n">
-        <v>5680</v>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>5.91%1,690,000</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>5.91%</t>
-        </is>
-      </c>
-      <c r="K211" t="n">
-        <v>1690000</v>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>-0.31%</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>3037欣興</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-4.82%1085</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-4.82%</t>
-        </is>
-      </c>
-      <c r="H212" t="n">
-        <v>1085</v>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>5.64%8,460,000</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>5.64%</t>
-        </is>
-      </c>
-      <c r="K212" t="n">
-        <v>8460000</v>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>1</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>3017奇鋐</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>-4.02%2865</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-4.02%</t>
-        </is>
-      </c>
-      <c r="H213" t="n">
-        <v>2865</v>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>5.23%3,000,000</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-      <c r="K213" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>-0.22%</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2454聯發科</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>+2.43%3790</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>+2.43%</t>
-        </is>
-      </c>
-      <c r="H214" t="n">
-        <v>3790</v>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>4.56%2,110,000</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>4.56%</t>
-        </is>
-      </c>
-      <c r="K214" t="n">
-        <v>2110000</v>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>1</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>2303聯電</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>+0.87%116.5</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>+0.87%</t>
-        </is>
-      </c>
-      <c r="H215" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>4.05%60,000,000</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="K215" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>6223旺矽</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-3.27%5465</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-3.27%</t>
-        </is>
-      </c>
-      <c r="H216" t="n">
-        <v>5465</v>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>3.63%1,100,000</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>3.63%</t>
-        </is>
-      </c>
-      <c r="K216" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>1</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>3653健策</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-3.66%5395</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-3.66%</t>
-        </is>
-      </c>
-      <c r="H217" t="n">
-        <v>5395</v>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>3.54%1,080,000</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="K217" t="n">
-        <v>1080000</v>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>2327國巨*</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-1.42%554</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-1.42%</t>
-        </is>
-      </c>
-      <c r="H218" t="n">
-        <v>554</v>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>3.21%9,785,000</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>3.21%</t>
-        </is>
-      </c>
-      <c r="K218" t="n">
-        <v>9785000</v>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2308台達電</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>+0.29%1750</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>+0.29%</t>
-        </is>
-      </c>
-      <c r="H219" t="n">
-        <v>1750</v>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>3.10%3,040,000</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>3.10%</t>
-        </is>
-      </c>
-      <c r="K219" t="n">
-        <v>3040000</v>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>2345智邦</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-3.33%2035</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-3.33%</t>
-        </is>
-      </c>
-      <c r="H220" t="n">
-        <v>2035</v>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>2.84%2,307,000</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>2.84%</t>
-        </is>
-      </c>
-      <c r="K220" t="n">
-        <v>2307000</v>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-0.51%587</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="H221" t="n">
-        <v>587</v>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>2.76%8,000,000</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>2.76%</t>
-        </is>
-      </c>
-      <c r="K221" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>6669緯穎</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-1.11%6255</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-1.11%</t>
-        </is>
-      </c>
-      <c r="H222" t="n">
-        <v>6255</v>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>2.26%610,000</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="K222" t="n">
-        <v>610000</v>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>3189景碩</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-4.7%811</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
-      <c r="H223" t="n">
-        <v>811</v>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2.11%4,250,000</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>2.11%</t>
-        </is>
-      </c>
-      <c r="K223" t="n">
-        <v>4250000</v>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:27</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>3008大立光</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>+1.72%5610</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="H224" t="n">
-        <v>5610</v>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>2.02%626,000</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>2.02%</t>
-        </is>
-      </c>
-      <c r="K224" t="n">
-        <v>626000</v>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>2</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>8046南電</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-5.02%1135</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>-5.02%</t>
-        </is>
-      </c>
-      <c r="H225" t="n">
-        <v>1135</v>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>1.84%2,640,000</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>1.84%</t>
-        </is>
-      </c>
-      <c r="K225" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>2</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>3443創意</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-0.53%5600</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
-      <c r="H226" t="n">
-        <v>5600</v>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>1.81%550,000</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>1.81%</t>
-        </is>
-      </c>
-      <c r="K226" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>2</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>5274信驊</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>-2.54%15350</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-2.54%</t>
-        </is>
-      </c>
-      <c r="H227" t="n">
-        <v>15350</v>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>1.65%179,500</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>1.65%</t>
-        </is>
-      </c>
-      <c r="K227" t="n">
-        <v>179500</v>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>2</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>6488環球晶</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-5.24%941</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-5.24%</t>
-        </is>
-      </c>
-      <c r="H228" t="n">
-        <v>941</v>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>1.63%2,800,000</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="K228" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>2</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>3665貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>+1.11%2275</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>+1.11%</t>
-        </is>
-      </c>
-      <c r="H229" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>1.58%1,200,000</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>1.58%</t>
-        </is>
-      </c>
-      <c r="K229" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>2</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>6274台燿</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-5.08%1495</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-5.08%</t>
-        </is>
-      </c>
-      <c r="H230" t="n">
-        <v>1495</v>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1.55%1,680,000</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>1.55%</t>
-        </is>
-      </c>
-      <c r="K230" t="n">
-        <v>1680000</v>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>2</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>2344華邦電</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>+2.55%181</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>+2.55%</t>
-        </is>
-      </c>
-      <c r="H231" t="n">
-        <v>181</v>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>1.55%15,000,000</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>1.55%</t>
-        </is>
-      </c>
-      <c r="K231" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>2</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>2360致茂</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-1.87%2100</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-1.87%</t>
-        </is>
-      </c>
-      <c r="H232" t="n">
-        <v>2100</v>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>1.25%1,000,000</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="K232" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>2</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>8996高力</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-3.96%1090</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>-3.96%</t>
-        </is>
-      </c>
-      <c r="H233" t="n">
-        <v>1090</v>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1.06%1,600,000</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="K233" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>2</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>1303南亞</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>+3.23%192</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>+3.23%</t>
-        </is>
-      </c>
-      <c r="H234" t="n">
-        <v>192</v>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>0.98%9,000,000</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="K234" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>2</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>6239力成</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-0.37%267.5</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-0.37%</t>
-        </is>
-      </c>
-      <c r="H235" t="n">
-        <v>267.5</v>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>0.84%5,360,000</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="K235" t="n">
-        <v>5360000</v>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>2</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>6805富世達</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>-4.59%1765</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-4.59%</t>
-        </is>
-      </c>
-      <c r="H236" t="n">
-        <v>1765</v>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>0.76%700,000</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="K236" t="n">
-        <v>700000</v>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>2</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>3450聯鈞</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-0.36%551</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-0.36%</t>
-        </is>
-      </c>
-      <c r="H237" t="n">
-        <v>551</v>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>0.58%1,800,000</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="K237" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>2</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>3533嘉澤</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-0.93%1595</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="H238" t="n">
-        <v>1595</v>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>0.49%525,000</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="K238" t="n">
-        <v>525000</v>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:28</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>2</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>7769鴻勁</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-0.77%6405</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="H239" t="n">
-        <v>6405</v>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>0.49%130,000</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="K239" t="n">
-        <v>130000</v>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>3</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>2317鴻海</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>-0.41%245.5</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H240" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>0.46%3,200,000</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="K240" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>3</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>3211順達</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>-1.27%350.5</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>-1.27%</t>
-        </is>
-      </c>
-      <c r="H241" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>0.42%2,000,000</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="K241" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>3</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>3583辛耘</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>-1.26%704</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>-1.26%</t>
-        </is>
-      </c>
-      <c r="H242" t="n">
-        <v>704</v>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>0.33%800,000</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="K242" t="n">
-        <v>800000</v>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>3</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>2337旺宏</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>+0.41%122.5</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="H243" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>0.32%4,500,000</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="K243" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>3</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>6442光聖</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>-1.93%1525</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H244" t="n">
-        <v>1525</v>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>0.20%225,000</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K244" t="n">
-        <v>225000</v>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>3</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>8358金居</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>+5.44%436</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>+5.44%</t>
-        </is>
-      </c>
-      <c r="H245" t="n">
-        <v>436</v>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>0.19%800,000</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K245" t="n">
-        <v>800000</v>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>3</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>4966譜瑞-KY</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-0.18%566</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="H246" t="n">
-        <v>566</v>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>0.17%500,000</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="K246" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>3</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>1560中砂</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>-2.72%679</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-2.72%</t>
-        </is>
-      </c>
-      <c r="H247" t="n">
-        <v>679</v>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>0.16%393,000</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K247" t="n">
-        <v>393000</v>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>3</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>2059川湖</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-3.88%13385</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>-3.88%</t>
-        </is>
-      </c>
-      <c r="H248" t="n">
-        <v>13385</v>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>0.16%20,000</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K248" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>3</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>2404漢唐</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>-1.4%1060</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>-1.4%</t>
-        </is>
-      </c>
-      <c r="H249" t="n">
-        <v>1060</v>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>0.16%250,000</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K249" t="n">
-        <v>250000</v>
-      </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>3</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>4958臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>-4.75%441</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-4.75%</t>
-        </is>
-      </c>
-      <c r="H250" t="n">
-        <v>441</v>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>0.14%500,000</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="K250" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>3</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>1717長興</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>+1.99%71.6</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>+1.99%</t>
-        </is>
-      </c>
-      <c r="H251" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>0.10%2,500,000</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="K251" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>3</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>3264欣銓</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-2.64%203</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>-2.64%</t>
-        </is>
-      </c>
-      <c r="H252" t="n">
-        <v>203</v>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>0.09%700,000</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-      <c r="K252" t="n">
-        <v>700000</v>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>3</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>2481強茂</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-3.97%133</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>-3.97%</t>
-        </is>
-      </c>
-      <c r="H253" t="n">
-        <v>133</v>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>0.06%700,000</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="K253" t="n">
-        <v>700000</v>
-      </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:29</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>3</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>6285啟碁</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>-0.63%235.5</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>-0.63%</t>
-        </is>
-      </c>
-      <c r="H254" t="n">
-        <v>235.5</v>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>0.05%350,000</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="K254" t="n">
-        <v>350000</v>
-      </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:31</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>4</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>2455全新</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>-1.46%406</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>-1.46%</t>
-        </is>
-      </c>
-      <c r="H255" t="n">
-        <v>406</v>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>0.05%200,000</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="K255" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:31</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>4</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>8299群聯</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>+4.01%2075</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>+4.01%</t>
-        </is>
-      </c>
-      <c r="H256" t="n">
-        <v>2075</v>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K256" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:31</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>4</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>6196帆宣</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-1.11%490.5</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-1.11%</t>
-        </is>
-      </c>
-      <c r="H257" t="n">
-        <v>490.5</v>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K257" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:31</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>4</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>2049上銀</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>-4.77%349</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>-4.77%</t>
-        </is>
-      </c>
-      <c r="H258" t="n">
-        <v>349</v>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K258" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:31</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>4</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>5347世界</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>-1.3%151.5</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="H259" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K259" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>2330台灣積體電路製造</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>+1.47%2410</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>+1.47%</t>
-        </is>
-      </c>
-      <c r="H260" t="n">
-        <v>2410</v>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>13.69%588,000</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>13.69%</t>
-        </is>
-      </c>
-      <c r="K260" t="n">
-        <v>588000</v>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>2376技嘉科技</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>-1.31%339.5</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>-1.31%</t>
-        </is>
-      </c>
-      <c r="H261" t="n">
-        <v>339.5</v>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>4.88%1,448,000</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
-      <c r="K261" t="n">
-        <v>1448000</v>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>2603長榮海運</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>+2.24%251.5</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>+2.24%</t>
-        </is>
-      </c>
-      <c r="H262" t="n">
-        <v>251.5</v>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>4.19%1,737,000</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>4.19%</t>
-        </is>
-      </c>
-      <c r="K262" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>4904遠傳電信</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>+0.49%102.5</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>+0.49%</t>
-        </is>
-      </c>
-      <c r="H263" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>3.83%3,832,000</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>3.83%</t>
-        </is>
-      </c>
-      <c r="K263" t="n">
-        <v>3832000</v>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>1</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>2412中華電信</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>0%136.5</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H264" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>3.79%2,828,000</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
-      <c r="K264" t="n">
-        <v>2828000</v>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>6669緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-1.11%6255</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>-1.11%</t>
-        </is>
-      </c>
-      <c r="H265" t="n">
-        <v>6255</v>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>3.29%53,000</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>3.29%</t>
-        </is>
-      </c>
-      <c r="K265" t="n">
-        <v>53000</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>1</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>3653健策精密工業</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>-3.66%5395</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-3.66%</t>
-        </is>
-      </c>
-      <c r="H266" t="n">
-        <v>5395</v>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>2.69%49,000</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-      <c r="K266" t="n">
-        <v>49000</v>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>1</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>7750新代科技</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>-9.96%2215</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-9.96%</t>
-        </is>
-      </c>
-      <c r="H267" t="n">
-        <v>2215</v>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>2.61%108,000</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="K267" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>2345智邦科技</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>-3.33%2035</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-3.33%</t>
-        </is>
-      </c>
-      <c r="H268" t="n">
-        <v>2035</v>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>2.56%124,000</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
-      <c r="K268" t="n">
-        <v>124000</v>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>1504東元電機</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-1.37%72.1</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-1.37%</t>
-        </is>
-      </c>
-      <c r="H269" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>2.49%3,473,000</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>2.49%</t>
-        </is>
-      </c>
-      <c r="K269" t="n">
-        <v>3473000</v>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>3105穩懋半導體</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-1.58%373</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-1.58%</t>
-        </is>
-      </c>
-      <c r="H270" t="n">
-        <v>373</v>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>2.44%656,000</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>2.44%</t>
-        </is>
-      </c>
-      <c r="K270" t="n">
-        <v>656000</v>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>3081聯亞光電工業</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>+5.04%2920</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>+5.04%</t>
-        </is>
-      </c>
-      <c r="H271" t="n">
-        <v>2920</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>2.26%83,000</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="K271" t="n">
-        <v>83000</v>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>+0.11%</t>
-        </is>
-      </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>6442光紅建聖</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>-1.93%1525</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H272" t="n">
-        <v>1525</v>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>2.26%148,000</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="K272" t="n">
-        <v>148000</v>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>2027大成不銹鋼工業</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-0.4%50.3</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>2.07%4,181,000</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>2.07%</t>
-        </is>
-      </c>
-      <c r="K273" t="n">
-        <v>4181000</v>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:37</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>3017奇鋐科技</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>-4.02%2865</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-4.02%</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>2865</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>1.99%68,000</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>1.99%</t>
-        </is>
-      </c>
-      <c r="K274" t="n">
-        <v>68000</v>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>2</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>7769鴻勁精密</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>-0.77%6405</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
-        <v>6405</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>1.96%31,000</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>1.96%</t>
-        </is>
-      </c>
-      <c r="K275" t="n">
-        <v>31000</v>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>2</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>3711日月光投資控股</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>-0.51%587</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
-        <v>587</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>1.94%335,000</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>1.94%</t>
-        </is>
-      </c>
-      <c r="K276" t="n">
-        <v>335000</v>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>2</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>2454聯發科技</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>+2.43%3790</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>+2.43%</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
-        <v>3790</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>1.81%50,000</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>1.81%</t>
-        </is>
-      </c>
-      <c r="K277" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>2</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>3037欣興電子</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>-4.82%1085</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>-4.82%</t>
-        </is>
-      </c>
-      <c r="H278" t="n">
-        <v>1085</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>1.79%160,000</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>1.79%</t>
-        </is>
-      </c>
-      <c r="K278" t="n">
-        <v>160000</v>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>2</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>2610中華航空</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>+2%20.4</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>+2%</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>1.72%8,783,000</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>1.72%</t>
-        </is>
-      </c>
-      <c r="K279" t="n">
-        <v>8783000</v>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>2</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>6147頎邦科技</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>-4.28%156.5</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-4.28%</t>
-        </is>
-      </c>
-      <c r="H280" t="n">
-        <v>156.5</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>1.63%1,019,000</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="K280" t="n">
-        <v>1019000</v>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>2</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>3036文曄科技</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>+0.24%206</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
-        <v>206</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>1.59%788,000</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="K281" t="n">
-        <v>788000</v>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>2</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>2059川湖科技</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>-3.88%13385</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>-3.88%</t>
-        </is>
-      </c>
-      <c r="H282" t="n">
-        <v>13385</v>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>1.50%11,000</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="K282" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>2</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>6446藥華醫藥</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>+1.82%1400</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>+1.82%</t>
-        </is>
-      </c>
-      <c r="H283" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>1.46%108,000</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="K283" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
-        <v>2</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>2308台達電子工業</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>+0.29%1750</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>+0.29%</t>
-        </is>
-      </c>
-      <c r="H284" t="n">
-        <v>1750</v>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>1.40%82,000</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>1.40%</t>
-        </is>
-      </c>
-      <c r="K284" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>2</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>2383台光電子材料</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>-5.1%5680</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>-5.1%</t>
-        </is>
-      </c>
-      <c r="H285" t="n">
-        <v>5680</v>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>1.35%23,000</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>1.35%</t>
-        </is>
-      </c>
-      <c r="K285" t="n">
-        <v>23000</v>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D286" t="n">
-        <v>2</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>1216統一企業</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>-0.9%77.5</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="H286" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>1.27%1,657,000</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>1.27%</t>
-        </is>
-      </c>
-      <c r="K286" t="n">
-        <v>1657000</v>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D287" t="n">
-        <v>2</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>8996高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>-3.96%1090</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>-3.96%</t>
-        </is>
-      </c>
-      <c r="H287" t="n">
-        <v>1090</v>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>1.26%113,000</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="K287" t="n">
-        <v>113000</v>
-      </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D288" t="n">
-        <v>2</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>2368金像電子（股）公司</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>-5.85%965</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>-5.85%</t>
-        </is>
-      </c>
-      <c r="H288" t="n">
-        <v>965</v>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>0.98%98,000</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="K288" t="n">
-        <v>98000</v>
-      </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:38</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D289" t="n">
-        <v>2</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>2408南亞科技</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>+2.13%528</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>+2.13%</t>
-        </is>
-      </c>
-      <c r="H289" t="n">
-        <v>528</v>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>0.98%193,000</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="K289" t="n">
-        <v>193000</v>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D290" t="n">
-        <v>3</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>2395研華</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>-3.57%649</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>-3.57%</t>
-        </is>
-      </c>
-      <c r="H290" t="n">
-        <v>649</v>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>0.96%146,000</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="K290" t="n">
-        <v>146000</v>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D291" t="n">
-        <v>3</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>6187萬潤科技</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>-5.53%1195</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>-5.53%</t>
-        </is>
-      </c>
-      <c r="H291" t="n">
-        <v>1195</v>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>0.69%56,000</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="K291" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>-0.04%</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D292" t="n">
-        <v>3</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>3008大立光電</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>+1.72%5610</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
-      <c r="H292" t="n">
-        <v>5610</v>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>0.65%12,000</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="K292" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D293" t="n">
-        <v>3</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>8046南亞電路板</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>-5.02%1135</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>-5.02%</t>
-        </is>
-      </c>
-      <c r="H293" t="n">
-        <v>1135</v>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>0.56%48,000</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="K293" t="n">
-        <v>48000</v>
-      </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D294" t="n">
-        <v>3</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>4958臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-4.75%441</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-4.75%</t>
-        </is>
-      </c>
-      <c r="H294" t="n">
-        <v>441</v>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>0.50%110,000</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="K294" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>3</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>2327國巨</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>-1.42%554</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>-1.42%</t>
-        </is>
-      </c>
-      <c r="H295" t="n">
-        <v>554</v>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>0.49%89,000</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="K295" t="n">
-        <v>89000</v>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>3</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>2344華邦電子</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>+2.55%181</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>+2.55%</t>
-        </is>
-      </c>
-      <c r="H296" t="n">
-        <v>181</v>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>0.42%243,000</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="K296" t="n">
-        <v>243000</v>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>3</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>8299群聯電子</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>+4.01%2075</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>+4.01%</t>
-        </is>
-      </c>
-      <c r="H297" t="n">
-        <v>2075</v>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>0.39%20,000</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K297" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>3</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>3131弘塑科技</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>-0.43%2310</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>-0.43%</t>
-        </is>
-      </c>
-      <c r="H298" t="n">
-        <v>2310</v>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>0.27%12,000</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="K298" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>3</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>2049上銀科技</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>-4.77%349</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>-4.77%</t>
-        </is>
-      </c>
-      <c r="H299" t="n">
-        <v>349</v>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>0.20%55,000</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K299" t="n">
-        <v>55000</v>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>3</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>1802台灣玻璃工業</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>-0.17%57.6</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
-      <c r="H300" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>0.20%357,000</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K300" t="n">
-        <v>357000</v>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>3</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>+1.11%2275</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>+1.11%</t>
-        </is>
-      </c>
-      <c r="H301" t="n">
-        <v>2275</v>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>0.20%9,000</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K301" t="n">
-        <v>9000</v>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>3</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>2303聯華電子</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>+0.87%116.5</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>+0.87%</t>
-        </is>
-      </c>
-      <c r="H302" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>0.19%171,000</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K302" t="n">
-        <v>171000</v>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D303" t="n">
-        <v>3</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>2881富邦金融控股</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>+4.69%134</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>+4.69%</t>
-        </is>
-      </c>
-      <c r="H303" t="n">
-        <v>134</v>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>0.19%154,000</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K303" t="n">
-        <v>154000</v>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:39</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D304" t="n">
-        <v>3</v>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>2891中國信託金融控股</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>+2.52%65</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>+2.52%</t>
-        </is>
-      </c>
-      <c r="H304" t="n">
-        <v>65</v>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>0.19%306,000</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K304" t="n">
-        <v>306000</v>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:41</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>4</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3529力旺電子</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>-2.49%2155</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>-2.49%</t>
-        </is>
-      </c>
-      <c r="H305" t="n">
-        <v>2155</v>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>0.17%8,000</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="K305" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:41</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>4</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>2317鴻海精密工業</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>-0.41%245.5</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H306" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>0.15%64,000</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>0.15%</t>
-        </is>
-      </c>
-      <c r="K306" t="n">
-        <v>64000</v>
-      </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:41</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>4</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>2360致茂電子</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>-1.87%2100</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>-1.87%</t>
-        </is>
-      </c>
-      <c r="H307" t="n">
-        <v>2100</v>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>0.10%5,000</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="K307" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:41</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>4</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>6488環球晶圓</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-5.24%941</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-5.24%</t>
-        </is>
-      </c>
-      <c r="H308" t="n">
-        <v>941</v>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>0.10%10,000</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="K308" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-08-21 16:07:41</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="D309" t="n">
-        <v>4</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>3189景碩科技</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>-4.7%811</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
-      <c r="H309" t="n">
-        <v>811</v>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>0.02%2,000</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="K309" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M309" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-21_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:43</t>
+          <t>2026-08-21 16:40:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:44</t>
+          <t>2026-08-21 16:40:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:45</t>
+          <t>2026-08-21 16:40:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:47</t>
+          <t>2026-08-21 16:40:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:02</t>
+          <t>2026-08-21 16:40:46</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:03</t>
+          <t>2026-08-21 16:40:48</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:04</t>
+          <t>2026-08-21 16:40:49</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:05</t>
+          <t>2026-08-21 16:40:50</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:11</t>
+          <t>2026-08-21 16:40:55</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:13</t>
+          <t>2026-08-21 16:40:56</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:14</t>
+          <t>2026-08-21 16:40:57</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-21 16:25:15</t>
+          <t>2026-08-21 16:40:59</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13194,6 +13194,3056 @@
         </is>
       </c>
       <c r="M209" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2330台積電</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>+1.47%2410</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>+1.47%</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>2410</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>16.66%12,000,000</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>16.66%</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2383台光電</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-5.1%5680</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-5.1%</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>5680</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>5.91%1,690,000</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="K211" t="n">
+        <v>1690000</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-4.82%1085</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-4.82%</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>1085</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>5.64%8,460,000</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>5.64%</t>
+        </is>
+      </c>
+      <c r="K212" t="n">
+        <v>8460000</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>3017奇鋐</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-4.02%2865</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-4.02%</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>2865</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>5.23%3,000,000</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>5.23%</t>
+        </is>
+      </c>
+      <c r="K213" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>+2.43%3790</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>+2.43%</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>3790</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>4.56%2,110,000</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>4.56%</t>
+        </is>
+      </c>
+      <c r="K214" t="n">
+        <v>2110000</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>+0.87%116.5</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>4.05%60,000,000</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="K215" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-3.27%5465</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-3.27%</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>5465</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>3.63%1,100,000</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="K216" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-3.66%5395</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-3.66%</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>5395</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>3.54%1,080,000</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2327國巨*</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-1.42%554</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>554</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>3.21%9,785,000</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>9785000</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>+0.29%1750</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>3.10%3,040,000</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>3040000</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-3.33%2035</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-3.33%</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>2035</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2.84%2,307,000</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>2307000</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-0.51%587</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>587</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2.76%8,000,000</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-1.11%6255</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>6255</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2.26%610,000</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>610000</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>3189景碩</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-4.7%811</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-4.7%</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>811</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2.11%4,250,000</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>4250000</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:04</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>+1.72%5610</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>5610</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2.02%626,000</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>626000</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>2</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-5.02%1135</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-5.02%</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>1135</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>1.84%2,640,000</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>2</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-0.53%5600</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>1.81%550,000</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>2</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-2.54%15350</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-2.54%</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>15350</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1.65%179,500</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>179500</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>2</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>6488環球晶</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-5.24%941</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-5.24%</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>941</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>1.63%2,800,000</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>2</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>+1.11%2275</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>+1.11%</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>2275</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>1.58%1,200,000</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>2</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-5.08%1495</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-5.08%</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>1495</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1.55%1,680,000</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2344華邦電</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>+2.55%181</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>+2.55%</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>181</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>1.55%15,000,000</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-1.87%2100</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-1.87%</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1.25%1,000,000</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>2</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-3.96%1090</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-3.96%</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>1090</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1.06%1,600,000</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>2</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1303南亞</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>+3.23%192</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>+3.23%</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>192</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>0.98%9,000,000</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>2</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>6239力成</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-0.37%267.5</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>0.84%5,360,000</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>5360000</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>2</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>6805富世達</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-4.59%1765</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-4.59%</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>1765</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>0.76%700,000</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>2</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>3450聯鈞</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-0.36%551</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>551</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>0.58%1,800,000</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>2</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>3533嘉澤</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-0.93%1595</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>1595</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>0.49%525,000</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>525000</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:05</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>2</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>7769鴻勁</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-0.77%6405</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>6405</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>0.49%130,000</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>3</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2317鴻海</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-0.41%245.5</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>0.46%3,200,000</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>3</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>3211順達</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-1.27%350.5</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>0.42%2,000,000</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>3</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>3583辛耘</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-1.26%704</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-1.26%</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>704</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>0.33%800,000</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>800000</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>3</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2337旺宏</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>+0.41%122.5</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>0.32%4,500,000</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>3</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>6442光聖</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-1.93%1525</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>1525</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>0.20%225,000</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>225000</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>3</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>8358金居</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>+5.44%436</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>+5.44%</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>436</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>0.19%800,000</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>800000</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>3</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>4966譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-0.18%566</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>566</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>0.17%500,000</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>3</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>1560中砂</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-2.72%679</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-2.72%</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>679</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>0.16%393,000</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>393000</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>3</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2059川湖</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-3.88%13385</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-3.88%</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>13385</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>0.16%20,000</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>3</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2404漢唐</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-1.4%1060</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>1060</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>0.16%250,000</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>3</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-4.75%441</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-4.75%</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>441</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>0.14%500,000</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>3</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1717長興</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>+1.99%71.6</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>+1.99%</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>0.10%2,500,000</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>3</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>3264欣銓</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-2.64%203</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-2.64%</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>203</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>0.09%700,000</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>3</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2481強茂</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-3.97%133</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-3.97%</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>133</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>0.06%700,000</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:07</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>3</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>6285啟碁</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-0.63%235.5</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>0.05%350,000</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:08</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-1.46%406</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>406</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>0.05%200,000</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:08</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>4</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>8299群聯</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>+4.01%2075</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>+4.01%</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>2075</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:08</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>6196帆宣</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-1.11%490.5</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:08</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2049上銀</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-4.77%349</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-4.77%</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>349</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:41:08</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>4</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-1.3%151.5</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
